--- a/artfynd/A 47948-2024 artfynd.xlsx
+++ b/artfynd/A 47948-2024 artfynd.xlsx
@@ -678,7 +678,7 @@
         <v>122744722</v>
       </c>
       <c r="B2" t="n">
-        <v>90958</v>
+        <v>90962</v>
       </c>
       <c r="C2" t="inlineStr">
         <is>

--- a/artfynd/A 47948-2024 artfynd.xlsx
+++ b/artfynd/A 47948-2024 artfynd.xlsx
@@ -678,7 +678,7 @@
         <v>122744722</v>
       </c>
       <c r="B2" t="n">
-        <v>90962</v>
+        <v>90970</v>
       </c>
       <c r="C2" t="inlineStr">
         <is>

--- a/artfynd/A 47948-2024 artfynd.xlsx
+++ b/artfynd/A 47948-2024 artfynd.xlsx
@@ -678,7 +678,7 @@
         <v>122744722</v>
       </c>
       <c r="B2" t="n">
-        <v>90970</v>
+        <v>90973</v>
       </c>
       <c r="C2" t="inlineStr">
         <is>

--- a/artfynd/A 47948-2024 artfynd.xlsx
+++ b/artfynd/A 47948-2024 artfynd.xlsx
@@ -678,7 +678,7 @@
         <v>122744722</v>
       </c>
       <c r="B2" t="n">
-        <v>90973</v>
+        <v>90975</v>
       </c>
       <c r="C2" t="inlineStr">
         <is>

--- a/artfynd/A 47948-2024 artfynd.xlsx
+++ b/artfynd/A 47948-2024 artfynd.xlsx
@@ -678,12 +678,7 @@
         <v>122744722</v>
       </c>
       <c r="B2" t="n">
-        <v>90975</v>
-      </c>
-      <c r="C2" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>91904</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
@@ -700,14 +695,10 @@
       </c>
       <c r="G2" t="inlineStr">
         <is>
-          <t>Porodaedalea chrysoloma</t>
-        </is>
-      </c>
-      <c r="H2" t="inlineStr">
-        <is>
-          <t>(Fr.) Fiasson &amp; Niemelä</t>
-        </is>
-      </c>
+          <t>Porodaedalea chrysoloma s.lat.</t>
+        </is>
+      </c>
+      <c r="H2" t="inlineStr"/>
       <c r="I2" t="inlineStr"/>
       <c r="P2" t="inlineStr">
         <is>
@@ -770,12 +761,12 @@
       </c>
       <c r="AX2" t="inlineStr">
         <is>
-          <t>Helene Andersson, Kristofer Wester</t>
+          <t>Kristofer Wester</t>
         </is>
       </c>
       <c r="AY2" t="inlineStr">
         <is>
-          <t xml:space="preserve">Naturvärdesinventering </t>
+          <t xml:space="preserve">Holmen Skog Naturvärdesinventering </t>
         </is>
       </c>
     </row>

--- a/artfynd/A 47948-2024 artfynd.xlsx
+++ b/artfynd/A 47948-2024 artfynd.xlsx
@@ -678,7 +678,7 @@
         <v>122744722</v>
       </c>
       <c r="B2" t="n">
-        <v>91909</v>
+        <v>91912</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>

--- a/artfynd/A 47948-2024 artfynd.xlsx
+++ b/artfynd/A 47948-2024 artfynd.xlsx
@@ -678,7 +678,7 @@
         <v>122744722</v>
       </c>
       <c r="B2" t="n">
-        <v>91912</v>
+        <v>91918</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>

--- a/artfynd/A 47948-2024 artfynd.xlsx
+++ b/artfynd/A 47948-2024 artfynd.xlsx
@@ -678,7 +678,7 @@
         <v>122744722</v>
       </c>
       <c r="B2" t="n">
-        <v>91918</v>
+        <v>91928</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>

--- a/artfynd/A 47948-2024 artfynd.xlsx
+++ b/artfynd/A 47948-2024 artfynd.xlsx
@@ -678,7 +678,7 @@
         <v>122744722</v>
       </c>
       <c r="B2" t="n">
-        <v>91928</v>
+        <v>91929</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
